--- a/mountain_car_continuous/DDPG/episode_rewards.xlsx
+++ b/mountain_car_continuous/DDPG/episode_rewards.xlsx
@@ -445,7 +445,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-32.66055453641837</v>
+        <v>-327.108945806091</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-32.79450901405394</v>
+        <v>-54.32077883987714</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>-33.42895278660621</v>
+        <v>-42.29075983622135</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-33.64042983397235</v>
+        <v>-24.71858176747377</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>-33.93549411876349</v>
+        <v>-1.205903119285985</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>-33.40516130229751</v>
+        <v>-89.50356427042068</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>-33.65750333844769</v>
+        <v>-32.63992434803982</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>-34.79985477762492</v>
+        <v>-5.355497965822051</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>-32.7374688265897</v>
+        <v>-9.939408511710624</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>-33.34287140256447</v>
+        <v>-3.287342583674156</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>-14.96560294887678</v>
+        <v>-17.98406649717854</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>88.52761183843619</v>
+        <v>-72.21751646271161</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>89.69292230473877</v>
+        <v>-18.18430365047366</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>-13.44508976689795</v>
+        <v>-49.09810214471612</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>88.66801853489565</v>
+        <v>-45.34374985951643</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>90.12105603217229</v>
+        <v>-10.56938354981054</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>82.07608748622637</v>
+        <v>51.28630007665824</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>82.36024184560716</v>
+        <v>-13.50338361721547</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>88.33055175245724</v>
+        <v>-355.2979530944494</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>90.17612874591529</v>
+        <v>-98.77463841757803</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>87.61448998898783</v>
+        <v>6.997268960364835</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>92.88770587393785</v>
+        <v>-72.29957829846879</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>90.58854674124143</v>
+        <v>-60.17391583851947</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>90.07972113487692</v>
+        <v>6.84656324181381</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>90.91707173249286</v>
+        <v>-11.15043261717366</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +645,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>81.43736748695119</v>
+        <v>9.926562962570852</v>
       </c>
     </row>
     <row r="28">
@@ -653,7 +653,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>82.75926216207085</v>
+        <v>-28.45679216914555</v>
       </c>
     </row>
     <row r="29">
@@ -661,7 +661,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>91.96921176912993</v>
+        <v>-25.08404766040442</v>
       </c>
     </row>
     <row r="30">
@@ -669,7 +669,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>89.3991118429922</v>
+        <v>-18.29034783201753</v>
       </c>
     </row>
     <row r="31">
@@ -677,7 +677,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>90.74597145444235</v>
+        <v>-73.10273797037844</v>
       </c>
     </row>
     <row r="32">
@@ -685,7 +685,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>90.20829999348048</v>
+        <v>-51.17910457258533</v>
       </c>
     </row>
     <row r="33">
@@ -693,7 +693,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>92.79977782173214</v>
+        <v>-368.224895192253</v>
       </c>
     </row>
     <row r="34">
@@ -701,7 +701,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>93.3108277236516</v>
+        <v>-11.18593333062525</v>
       </c>
     </row>
     <row r="35">
@@ -709,7 +709,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>93.42084197888438</v>
+        <v>-33.55464759728871</v>
       </c>
     </row>
     <row r="36">
@@ -717,7 +717,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>91.43467492668189</v>
+        <v>-89.77176153416475</v>
       </c>
     </row>
     <row r="37">
@@ -725,7 +725,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>90.19347383093385</v>
+        <v>-42.83506333246212</v>
       </c>
     </row>
     <row r="38">
@@ -733,7 +733,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>89.48130360439413</v>
+        <v>-2.56300482752273</v>
       </c>
     </row>
     <row r="39">
@@ -741,7 +741,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>90.01527987158674</v>
+        <v>3.499421256059855</v>
       </c>
     </row>
     <row r="40">
@@ -749,7 +749,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>92.6697078367514</v>
+        <v>-19.8314239261148</v>
       </c>
     </row>
     <row r="41">
@@ -757,7 +757,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>90.71864468297821</v>
+        <v>-276.771633885082</v>
       </c>
     </row>
     <row r="42">
@@ -765,7 +765,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>89.52099285640729</v>
+        <v>-6.436579729623061</v>
       </c>
     </row>
     <row r="43">
@@ -773,7 +773,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>93.54558357151441</v>
+        <v>-14.96983060517869</v>
       </c>
     </row>
     <row r="44">
@@ -781,7 +781,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>91.14131972251072</v>
+        <v>-5.790459076658543</v>
       </c>
     </row>
     <row r="45">
@@ -789,7 +789,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>89.02315712607184</v>
+        <v>-39.83435448296504</v>
       </c>
     </row>
     <row r="46">
@@ -797,7 +797,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>92.43927093245237</v>
+        <v>7.625735372215728</v>
       </c>
     </row>
     <row r="47">
@@ -805,7 +805,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>92.24130730276524</v>
+        <v>-11.36868218387742</v>
       </c>
     </row>
     <row r="48">
@@ -813,7 +813,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>92.47942154418392</v>
+        <v>-7.729682654256761</v>
       </c>
     </row>
     <row r="49">
@@ -821,7 +821,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>93.8554280774441</v>
+        <v>-35.902091422475</v>
       </c>
     </row>
     <row r="50">
@@ -829,7 +829,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>93.92863196299365</v>
+        <v>-41.34672728374243</v>
       </c>
     </row>
     <row r="51">
@@ -837,7 +837,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>92.61717193609751</v>
+        <v>-300.8959328691703</v>
       </c>
     </row>
     <row r="52">
@@ -845,7 +845,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>90.55273608721838</v>
+        <v>-9.308552423701109</v>
       </c>
     </row>
     <row r="53">
@@ -853,7 +853,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>92.18443971194336</v>
+        <v>-336.0413266615665</v>
       </c>
     </row>
     <row r="54">
@@ -861,7 +861,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>91.11364780151024</v>
+        <v>-45.45736523173015</v>
       </c>
     </row>
     <row r="55">
@@ -869,7 +869,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>88.67492412719204</v>
+        <v>-119.7106231466838</v>
       </c>
     </row>
     <row r="56">
@@ -877,7 +877,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>89.10831907148041</v>
+        <v>-475.7783148382803</v>
       </c>
     </row>
     <row r="57">
@@ -885,7 +885,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>90.73344373186201</v>
+        <v>-38.26011936229528</v>
       </c>
     </row>
     <row r="58">
@@ -893,7 +893,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>91.84534771500427</v>
+        <v>-1998.88383901615</v>
       </c>
     </row>
     <row r="59">
@@ -901,7 +901,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>93.83688214590946</v>
+        <v>-2013.989189351898</v>
       </c>
     </row>
     <row r="60">
@@ -909,7 +909,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>91.92341166606678</v>
+        <v>-1976.219406127383</v>
       </c>
     </row>
     <row r="61">
@@ -917,7 +917,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>89.94170128677415</v>
+        <v>-46.81916855643127</v>
       </c>
     </row>
     <row r="62">
@@ -925,7 +925,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>90.34370727399538</v>
+        <v>-17.86762046080751</v>
       </c>
     </row>
     <row r="63">
@@ -933,7 +933,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>90.91119351620031</v>
+        <v>-86.10045250136039</v>
       </c>
     </row>
     <row r="64">
@@ -941,7 +941,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>92.32654320007852</v>
+        <v>-38.715654383195</v>
       </c>
     </row>
     <row r="65">
@@ -949,7 +949,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>91.19577033830043</v>
+        <v>-128.4329167523101</v>
       </c>
     </row>
     <row r="66">
@@ -957,7 +957,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>93.52657866120383</v>
+        <v>-1967.476795484353</v>
       </c>
     </row>
     <row r="67">
@@ -965,7 +965,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>92.09703470668033</v>
+        <v>-50.78830411471039</v>
       </c>
     </row>
     <row r="68">
@@ -973,7 +973,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>91.53007046654922</v>
+        <v>-140.5006650937496</v>
       </c>
     </row>
     <row r="69">
@@ -981,7 +981,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>92.11453128340744</v>
+        <v>-29.57129807073349</v>
       </c>
     </row>
     <row r="70">
@@ -989,7 +989,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>92.73887167305813</v>
+        <v>-23.36098395124871</v>
       </c>
     </row>
     <row r="71">
@@ -997,7 +997,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>91.00229239558392</v>
+        <v>-114.8777359152468</v>
       </c>
     </row>
     <row r="72">
@@ -1005,7 +1005,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>93.74243513824729</v>
+        <v>-77.23496130406791</v>
       </c>
     </row>
     <row r="73">
@@ -1013,7 +1013,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>94.57429730974243</v>
+        <v>-45.33909264825651</v>
       </c>
     </row>
     <row r="74">
@@ -1021,7 +1021,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>93.76634199219805</v>
+        <v>-28.85826899570641</v>
       </c>
     </row>
     <row r="75">
@@ -1029,7 +1029,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>94.30402421156103</v>
+        <v>-19.18612867543463</v>
       </c>
     </row>
     <row r="76">
@@ -1037,7 +1037,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>93.37079703497358</v>
+        <v>-68.71192383925172</v>
       </c>
     </row>
     <row r="77">
@@ -1045,7 +1045,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>91.28849396283341</v>
+        <v>-14.13912570645772</v>
       </c>
     </row>
     <row r="78">
@@ -1053,7 +1053,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>94.5707818832097</v>
+        <v>-34.71224761281807</v>
       </c>
     </row>
     <row r="79">
@@ -1061,7 +1061,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>91.41090443202783</v>
+        <v>-42.85708131481485</v>
       </c>
     </row>
     <row r="80">
@@ -1069,7 +1069,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>94.19563311350298</v>
+        <v>-136.4327984574529</v>
       </c>
     </row>
     <row r="81">
@@ -1077,7 +1077,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>94.40881661831703</v>
+        <v>-26.62373493429448</v>
       </c>
     </row>
     <row r="82">
@@ -1085,7 +1085,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>94.30559245389007</v>
+        <v>-148.3610507972826</v>
       </c>
     </row>
     <row r="83">
@@ -1093,7 +1093,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>94.28333275740924</v>
+        <v>-13.2971407346174</v>
       </c>
     </row>
     <row r="84">
@@ -1101,7 +1101,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>94.68124880100525</v>
+        <v>-146.8584539603557</v>
       </c>
     </row>
     <row r="85">
@@ -1109,7 +1109,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>94.69672633894479</v>
+        <v>-51.45186952535889</v>
       </c>
     </row>
     <row r="86">
@@ -1117,7 +1117,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>95.04876161833899</v>
+        <v>-152.7593729111042</v>
       </c>
     </row>
     <row r="87">
@@ -1125,7 +1125,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>94.10367785761315</v>
+        <v>-64.00577267553268</v>
       </c>
     </row>
     <row r="88">
@@ -1133,7 +1133,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>94.28896660987016</v>
+        <v>-53.82284488767155</v>
       </c>
     </row>
     <row r="89">
@@ -1141,7 +1141,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>95.16823339207481</v>
+        <v>-1931.63223484452</v>
       </c>
     </row>
     <row r="90">
@@ -1149,7 +1149,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>95.12870294543211</v>
+        <v>-24.9071695418785</v>
       </c>
     </row>
     <row r="91">
@@ -1157,7 +1157,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>95.70431648153047</v>
+        <v>-51.09168532387761</v>
       </c>
     </row>
     <row r="92">
@@ -1165,7 +1165,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>90.59706096508384</v>
+        <v>-23.55311936936499</v>
       </c>
     </row>
     <row r="93">
@@ -1173,7 +1173,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>87.4384896326912</v>
+        <v>-198.2603411589878</v>
       </c>
     </row>
     <row r="94">
@@ -1181,7 +1181,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>94.72836499127756</v>
+        <v>-60.40579159755816</v>
       </c>
     </row>
     <row r="95">
@@ -1189,7 +1189,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>94.58875328420137</v>
+        <v>-222.8874116348733</v>
       </c>
     </row>
     <row r="96">
@@ -1197,7 +1197,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>91.95176922631524</v>
+        <v>-85.67245840789448</v>
       </c>
     </row>
     <row r="97">
@@ -1205,7 +1205,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>94.04781376591924</v>
+        <v>-140.1948934819841</v>
       </c>
     </row>
     <row r="98">
@@ -1213,7 +1213,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>92.63671235335616</v>
+        <v>-69.28747173216077</v>
       </c>
     </row>
     <row r="99">
@@ -1221,7 +1221,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>92.6834998373354</v>
+        <v>-128.4248536491307</v>
       </c>
     </row>
     <row r="100">
@@ -1229,7 +1229,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>93.78944702250546</v>
+        <v>-98.03789102200861</v>
       </c>
     </row>
     <row r="101">
@@ -1237,7 +1237,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>93.3978779352265</v>
+        <v>-73.23573704066784</v>
       </c>
     </row>
     <row r="102">
@@ -1245,7 +1245,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>79.21772580656138</v>
+        <v>-236.7078208380152</v>
       </c>
     </row>
     <row r="103">
@@ -1253,7 +1253,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>92.85948300843781</v>
+        <v>-51.61821936034806</v>
       </c>
     </row>
     <row r="104">
@@ -1261,7 +1261,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>94.21247191282713</v>
+        <v>-100.7532467129202</v>
       </c>
     </row>
     <row r="105">
@@ -1269,7 +1269,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>92.86212759087421</v>
+        <v>-26.48312631039068</v>
       </c>
     </row>
     <row r="106">
@@ -1277,7 +1277,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>94.82911948269378</v>
+        <v>-24.54716026711053</v>
       </c>
     </row>
     <row r="107">
@@ -1285,7 +1285,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>93.80217139232462</v>
+        <v>-1958.089733156439</v>
       </c>
     </row>
     <row r="108">
@@ -1293,7 +1293,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>93.41600006187166</v>
+        <v>-118.5600328872831</v>
       </c>
     </row>
     <row r="109">
@@ -1301,7 +1301,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>94.4358732597934</v>
+        <v>-52.50172676528847</v>
       </c>
     </row>
     <row r="110">
@@ -1309,7 +1309,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>94.03576345702999</v>
+        <v>-1987.720011243511</v>
       </c>
     </row>
     <row r="111">
@@ -1317,7 +1317,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>93.66472098763533</v>
+        <v>-52.7217811606947</v>
       </c>
     </row>
     <row r="112">
@@ -1325,7 +1325,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>93.87350406196924</v>
+        <v>-36.23642431223688</v>
       </c>
     </row>
     <row r="113">
@@ -1333,7 +1333,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>94.67888864606377</v>
+        <v>-1994.452030809537</v>
       </c>
     </row>
     <row r="114">
@@ -1341,7 +1341,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>93.68459053215872</v>
+        <v>-1651.15473652386</v>
       </c>
     </row>
     <row r="115">
@@ -1349,7 +1349,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>93.95124956737509</v>
+        <v>-110.7163116303238</v>
       </c>
     </row>
     <row r="116">
@@ -1357,7 +1357,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>93.46346432400392</v>
+        <v>-1857.877610210542</v>
       </c>
     </row>
     <row r="117">
@@ -1365,7 +1365,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>94.79142606820263</v>
+        <v>-121.5455860641729</v>
       </c>
     </row>
     <row r="118">
@@ -1373,7 +1373,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>94.00204450561959</v>
+        <v>-55.78056997014153</v>
       </c>
     </row>
     <row r="119">
@@ -1381,7 +1381,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>93.54800086586276</v>
+        <v>-133.241178114598</v>
       </c>
     </row>
     <row r="120">
@@ -1389,7 +1389,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>93.67893293879337</v>
+        <v>-104.31313417442</v>
       </c>
     </row>
     <row r="121">
@@ -1397,7 +1397,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>94.24038513754462</v>
+        <v>-158.0461164082046</v>
       </c>
     </row>
     <row r="122">
@@ -1405,7 +1405,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>93.18450891928066</v>
+        <v>-77.21051685888857</v>
       </c>
     </row>
     <row r="123">
@@ -1413,7 +1413,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>90.7069752318919</v>
+        <v>-103.812292133259</v>
       </c>
     </row>
     <row r="124">
@@ -1421,7 +1421,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>93.04298985667216</v>
+        <v>-122.7428577424552</v>
       </c>
     </row>
     <row r="125">
@@ -1429,7 +1429,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>93.90829722017276</v>
+        <v>-103.0269113921831</v>
       </c>
     </row>
     <row r="126">
@@ -1437,7 +1437,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>92.35591071759202</v>
+        <v>-147.0300107216256</v>
       </c>
     </row>
     <row r="127">
@@ -1445,7 +1445,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>92.75353450987174</v>
+        <v>-40.66454567361111</v>
       </c>
     </row>
     <row r="128">
@@ -1453,7 +1453,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>92.96904180798373</v>
+        <v>-63.04718683674344</v>
       </c>
     </row>
     <row r="129">
@@ -1461,7 +1461,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>94.30829075910864</v>
+        <v>-35.14525872700101</v>
       </c>
     </row>
     <row r="130">
@@ -1469,7 +1469,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>94.54622891495309</v>
+        <v>-20.17699962104801</v>
       </c>
     </row>
     <row r="131">
@@ -1477,7 +1477,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>94.27129662000833</v>
+        <v>-155.4686789846904</v>
       </c>
     </row>
     <row r="132">
@@ -1485,7 +1485,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>94.04971324616891</v>
+        <v>-92.5388084146462</v>
       </c>
     </row>
     <row r="133">
@@ -1493,7 +1493,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>93.800497238662</v>
+        <v>-4.162000137478309</v>
       </c>
     </row>
     <row r="134">
@@ -1501,7 +1501,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>93.86440866274141</v>
+        <v>-85.35137753036324</v>
       </c>
     </row>
     <row r="135">
@@ -1509,7 +1509,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>93.58455094393855</v>
+        <v>-246.7445194034827</v>
       </c>
     </row>
     <row r="136">
@@ -1517,7 +1517,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="n">
-        <v>93.52715951425115</v>
+        <v>-15.94094764388421</v>
       </c>
     </row>
     <row r="137">
@@ -1525,7 +1525,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="n">
-        <v>94.4284902097224</v>
+        <v>-1882.532231765546</v>
       </c>
     </row>
     <row r="138">
@@ -1533,7 +1533,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>93.99227422682081</v>
+        <v>-130.8304102507513</v>
       </c>
     </row>
     <row r="139">
@@ -1541,7 +1541,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>94.1380723848755</v>
+        <v>-1656.37157861514</v>
       </c>
     </row>
     <row r="140">
@@ -1549,7 +1549,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>93.87255162130619</v>
+        <v>-1641.642989813913</v>
       </c>
     </row>
     <row r="141">
@@ -1557,7 +1557,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>94.5018314474989</v>
+        <v>-358.4899400540498</v>
       </c>
     </row>
     <row r="142">
@@ -1565,7 +1565,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>95.23425941810613</v>
+        <v>-25.25723829547217</v>
       </c>
     </row>
     <row r="143">
@@ -1573,7 +1573,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>93.34902865601477</v>
+        <v>-28.68963238399492</v>
       </c>
     </row>
     <row r="144">
@@ -1581,7 +1581,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>93.19193323124711</v>
+        <v>-18.60748079952371</v>
       </c>
     </row>
     <row r="145">
@@ -1589,7 +1589,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>93.91516663990178</v>
+        <v>-41.50542883108919</v>
       </c>
     </row>
     <row r="146">
@@ -1597,7 +1597,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>93.36995777042466</v>
+        <v>-54.42312943401315</v>
       </c>
     </row>
     <row r="147">
@@ -1605,7 +1605,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>93.815012119906</v>
+        <v>-97.90094761949872</v>
       </c>
     </row>
     <row r="148">
@@ -1613,7 +1613,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>94.41956151284066</v>
+        <v>-210.6968929128203</v>
       </c>
     </row>
     <row r="149">
@@ -1621,7 +1621,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>94.10436214446683</v>
+        <v>-50.01930562674339</v>
       </c>
     </row>
     <row r="150">
@@ -1629,7 +1629,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>94.82566260808485</v>
+        <v>-59.61364687001988</v>
       </c>
     </row>
     <row r="151">
@@ -1637,7 +1637,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>93.64478437864555</v>
+        <v>-56.91551298421602</v>
       </c>
     </row>
     <row r="152">
@@ -1645,7 +1645,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>94.4141259037112</v>
+        <v>-37.40696934517833</v>
       </c>
     </row>
     <row r="153">
@@ -1653,7 +1653,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>93.10978016551896</v>
+        <v>-223.8033975213391</v>
       </c>
     </row>
     <row r="154">
@@ -1661,7 +1661,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>93.50569493516453</v>
+        <v>-51.60069577124361</v>
       </c>
     </row>
     <row r="155">
@@ -1669,7 +1669,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>94.57511827354534</v>
+        <v>-19.00556711170996</v>
       </c>
     </row>
     <row r="156">
@@ -1677,7 +1677,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>94.13077998370308</v>
+        <v>-80.56335525235075</v>
       </c>
     </row>
     <row r="157">
@@ -1685,7 +1685,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>93.64171160577772</v>
+        <v>-9.82366479661181</v>
       </c>
     </row>
     <row r="158">
@@ -1693,7 +1693,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>89.15400145725602</v>
+        <v>-1579.301027445358</v>
       </c>
     </row>
     <row r="159">
@@ -1701,7 +1701,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>93.78069260203328</v>
+        <v>-67.89446917005466</v>
       </c>
     </row>
     <row r="160">
@@ -1709,7 +1709,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>93.95246246407862</v>
+        <v>-54.17401801024842</v>
       </c>
     </row>
     <row r="161">
@@ -1717,7 +1717,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>94.17907636858659</v>
+        <v>-13.85472729212175</v>
       </c>
     </row>
     <row r="162">
@@ -1725,7 +1725,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>93.56024077219486</v>
+        <v>-79.47828816862086</v>
       </c>
     </row>
     <row r="163">
@@ -1733,7 +1733,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>94.33248786554321</v>
+        <v>-153.7428408983964</v>
       </c>
     </row>
     <row r="164">
@@ -1741,7 +1741,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>93.24266349521106</v>
+        <v>-74.17758505378018</v>
       </c>
     </row>
     <row r="165">
@@ -1749,7 +1749,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>94.60004241632132</v>
+        <v>-44.86882743803773</v>
       </c>
     </row>
     <row r="166">
@@ -1757,7 +1757,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>93.62167110333571</v>
+        <v>-120.4894160552142</v>
       </c>
     </row>
     <row r="167">
@@ -1765,7 +1765,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>95.15522769655023</v>
+        <v>-86.17349867479976</v>
       </c>
     </row>
     <row r="168">
@@ -1773,7 +1773,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>93.814561665231</v>
+        <v>-18.55240797696755</v>
       </c>
     </row>
     <row r="169">
@@ -1781,7 +1781,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>93.8386181771664</v>
+        <v>-30.54037986072254</v>
       </c>
     </row>
     <row r="170">
@@ -1789,7 +1789,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>93.6766193577554</v>
+        <v>-62.92068256908302</v>
       </c>
     </row>
     <row r="171">
@@ -1797,7 +1797,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>93.73978480667796</v>
+        <v>-72.94318659317968</v>
       </c>
     </row>
     <row r="172">
@@ -1805,7 +1805,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>91.02206774964353</v>
+        <v>-35.5226932500989</v>
       </c>
     </row>
     <row r="173">
@@ -1813,7 +1813,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>93.84202534429706</v>
+        <v>-63.31875710115311</v>
       </c>
     </row>
     <row r="174">
@@ -1821,7 +1821,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>92.40174065051855</v>
+        <v>-92.32717789487887</v>
       </c>
     </row>
     <row r="175">
@@ -1829,7 +1829,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>94.38149150725923</v>
+        <v>-36.94244265852777</v>
       </c>
     </row>
     <row r="176">
@@ -1837,7 +1837,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>91.11274704785995</v>
+        <v>-22.34069548496685</v>
       </c>
     </row>
     <row r="177">
@@ -1845,7 +1845,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>92.6507977090061</v>
+        <v>-1517.665872505053</v>
       </c>
     </row>
     <row r="178">
@@ -1853,7 +1853,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="n">
-        <v>93.08672096119471</v>
+        <v>-65.79362962647103</v>
       </c>
     </row>
     <row r="179">
@@ -1861,7 +1861,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="n">
-        <v>90.59950995179346</v>
+        <v>-73.96070182123671</v>
       </c>
     </row>
     <row r="180">
@@ -1869,7 +1869,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>94.33795725279045</v>
+        <v>-149.57876612974</v>
       </c>
     </row>
     <row r="181">
@@ -1877,7 +1877,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>88.35788951512603</v>
+        <v>-2.209427707977635</v>
       </c>
     </row>
     <row r="182">
@@ -1885,7 +1885,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>93.87239114146898</v>
+        <v>-74.71275242101586</v>
       </c>
     </row>
     <row r="183">
@@ -1893,7 +1893,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="n">
-        <v>93.99127357453793</v>
+        <v>-222.5579689423332</v>
       </c>
     </row>
     <row r="184">
@@ -1901,7 +1901,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="n">
-        <v>90.95352942133977</v>
+        <v>-59.4871566252021</v>
       </c>
     </row>
     <row r="185">
@@ -1909,7 +1909,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>90.07236152831263</v>
+        <v>-27.2410969577253</v>
       </c>
     </row>
     <row r="186">
@@ -1917,7 +1917,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>88.09422198811112</v>
+        <v>-202.2941066368903</v>
       </c>
     </row>
     <row r="187">
@@ -1925,7 +1925,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>89.33614431165475</v>
+        <v>-59.78920207422109</v>
       </c>
     </row>
     <row r="188">
@@ -1933,7 +1933,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="n">
-        <v>88.86474225831969</v>
+        <v>-7.667214264908012</v>
       </c>
     </row>
     <row r="189">
@@ -1941,7 +1941,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>89.60358657822606</v>
+        <v>-26.44284909330883</v>
       </c>
     </row>
     <row r="190">
@@ -1949,7 +1949,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>91.68193197856377</v>
+        <v>-47.04567373137163</v>
       </c>
     </row>
     <row r="191">
@@ -1957,7 +1957,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>90.21051420748759</v>
+        <v>-1491.974194932005</v>
       </c>
     </row>
     <row r="192">
@@ -1965,7 +1965,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>89.37741839794346</v>
+        <v>-14.22166089138797</v>
       </c>
     </row>
     <row r="193">
@@ -1973,7 +1973,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="n">
-        <v>94.30903166983259</v>
+        <v>-220.0771792401458</v>
       </c>
     </row>
     <row r="194">
@@ -1981,7 +1981,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>91.28444532697809</v>
+        <v>-179.3396959674857</v>
       </c>
     </row>
     <row r="195">
@@ -1989,7 +1989,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>89.71606740405079</v>
+        <v>-14.3663423639283</v>
       </c>
     </row>
     <row r="196">
@@ -1997,7 +1997,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>91.080290862609</v>
+        <v>-32.10789740876439</v>
       </c>
     </row>
     <row r="197">
@@ -2005,7 +2005,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>90.12575186717673</v>
+        <v>-37.91769270369075</v>
       </c>
     </row>
     <row r="198">
@@ -2013,7 +2013,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>93.05843189611838</v>
+        <v>-1508.440573433461</v>
       </c>
     </row>
     <row r="199">
@@ -2021,7 +2021,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>91.37605099856438</v>
+        <v>-49.06471970889699</v>
       </c>
     </row>
     <row r="200">
@@ -2029,7 +2029,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="n">
-        <v>92.22884883274743</v>
+        <v>-66.70327762246512</v>
       </c>
     </row>
     <row r="201">
@@ -2037,7 +2037,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>90.36415395883706</v>
+        <v>-58.13473661539634</v>
       </c>
     </row>
   </sheetData>
